--- a/output/pdf_financials_xlsx/CRT.UN.xlsx
+++ b/output/pdf_financials_xlsx/CRT.UN.xlsx
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>30.996</v>
+        <v>30.913</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>318.261</v>
+        <v>317.911</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>234.48</v>
+        <v>234.248</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>259.079</v>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>30.996</v>
+        <v>30.913</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>318.261</v>
+        <v>317.911</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>234.48</v>
+        <v>234.248</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>259.079</v>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRT.UN.xlsx
+++ b/output/pdf_financials_xlsx/CRT.UN.xlsx
@@ -3396,19 +3396,19 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.649</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>1.318</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
     </row>
     <row r="71">
@@ -3436,19 +3436,19 @@
         <v>14.995</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>79.3</v>
+        <v>80.367</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>99.884</v>
+        <v>100.533</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>98.5</v>
+        <v>99.818</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>195.8</v>
+        <v>197.432</v>
       </c>
     </row>
     <row r="72">
@@ -3596,19 +3596,19 @@
         <v>84.04600000000001</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>224.055</v>
+        <v>222.988</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>178.776</v>
+        <v>178.127</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>332.934</v>
+        <v>332.011</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>520.508</v>
+        <v>519.1900000000001</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>329.447</v>
+        <v>327.815</v>
       </c>
     </row>
     <row r="76">
@@ -3800,19 +3800,19 @@
         <v>0.004860759263887525</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.041870788812525</v>
+        <v>0.04216088037760297</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.05280843066148303</v>
+        <v>0.05297800752670444</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.02603508682563844</v>
+        <v>0.02627496609073985</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.04815779425703659</v>
+        <v>0.04847935531643145</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.07297066663764752</v>
+        <v>0.07334066066605273</v>
       </c>
     </row>
     <row r="81">
@@ -5752,10 +5752,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>-120.535</v>
@@ -5763,10 +5761,8 @@
       <c r="D129" s="3" t="n">
         <v>-140.6</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>228.166</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>-33.458</v>
@@ -5797,7 +5793,7 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>297.436</v>
+        <v>257.661</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>46.999</v>
@@ -5877,7 +5873,7 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>-250.437</v>
+        <v>-210.662</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-44.289</v>
@@ -5996,21 +5992,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>39.775</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>233.789</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>265.4</v>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>265.168</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>275.584</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>317.154</v>
@@ -7340,7 +7332,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -12504,7 +12500,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -16730,7 +16730,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>39.775</v>
       </c>
